--- a/data/trans_bre/P20-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P20-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,42</t>
+          <t>-1,94; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,82</t>
+          <t>1,79; 10,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,36</t>
+          <t>-0,3; 8,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,77</t>
+          <t>-2,16; 3,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 118,68</t>
+          <t>-33,78; 133,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,53; 313,52</t>
+          <t>18,43; 325,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 165,16</t>
+          <t>-9,85; 174,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 81,6</t>
+          <t>-28,43; 84,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 7,19</t>
+          <t>0,22; 7,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,66</t>
+          <t>2,33; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,16</t>
+          <t>0,06; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,54</t>
+          <t>-0,17; 5,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 248,46</t>
+          <t>1,54; 301,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 372,58</t>
+          <t>40,91; 407,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 215,96</t>
+          <t>-2,32; 195,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 162,32</t>
+          <t>-7,76; 168,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 12,05</t>
+          <t>1,49; 11,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,62</t>
+          <t>-2,77; 5,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 9,69</t>
+          <t>-1,05; 9,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 13,11</t>
+          <t>0,34; 12,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,59; 416,08</t>
+          <t>35,91; 400,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 85,49</t>
+          <t>-30,01; 82,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 180,66</t>
+          <t>-17,02; 191,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 552,92</t>
+          <t>0,75; 556,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,91</t>
+          <t>1,81; 6,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,99</t>
+          <t>1,61; 6,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,91</t>
+          <t>2,22; 7,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,93</t>
+          <t>-4,01; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,19; 187,14</t>
+          <t>34,06; 191,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 129,1</t>
+          <t>20,72; 125,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,98; 181,75</t>
+          <t>37,83; 181,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 38,13</t>
+          <t>-54,89; 39,2</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 6,07</t>
+          <t>-0,47; 5,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,43</t>
+          <t>-0,57; 6,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,09</t>
+          <t>0,36; 5,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -0,76</t>
+          <t>-6,42; -0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 205,11</t>
+          <t>-15,05; 201,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 114,94</t>
+          <t>-6,55; 109,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 203,71</t>
+          <t>6,47; 232,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,44; -9,66</t>
+          <t>-63,46; -13,8</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,93</t>
+          <t>2,49; 6,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,92</t>
+          <t>1,78; 7,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,28</t>
+          <t>0,16; 5,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,85</t>
+          <t>1,8; 5,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,52; 2049,47</t>
+          <t>45,1; 2149,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,41; 480,0</t>
+          <t>24,54; 456,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 322,65</t>
+          <t>2,32; 313,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 1844,8</t>
+          <t>16,91; 1787,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,5</t>
+          <t>2,2; 4,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,96</t>
+          <t>2,15; 4,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,09</t>
+          <t>1,62; 4,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,87</t>
+          <t>-1,21; 1,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,23; 121,6</t>
+          <t>45,49; 119,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,13; 92,0</t>
+          <t>31,0; 85,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,55; 93,53</t>
+          <t>30,74; 97,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 41,86</t>
+          <t>-18,91; 37,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P20-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,97</t>
+          <t>-2,09; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,84</t>
+          <t>2,19; 10,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,07</t>
+          <t>-0,19; 7,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,81</t>
+          <t>-1,94; 4,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 133,87</t>
+          <t>-34,82; 119,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 325,79</t>
+          <t>27,66; 306,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 174,83</t>
+          <t>-5,06; 171,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 84,53</t>
+          <t>-25,75; 89,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 7,71</t>
+          <t>0,11; 7,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 10,05</t>
+          <t>2,14; 9,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,53</t>
+          <t>-0,07; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,93</t>
+          <t>0,23; 6,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 301,49</t>
+          <t>-4,4; 245,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,91; 407,54</t>
+          <t>31,79; 360,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 195,43</t>
+          <t>-3,64; 202,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 168,14</t>
+          <t>3,29; 187,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 11,97</t>
+          <t>1,72; 11,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,18</t>
+          <t>-2,9; 5,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,72</t>
+          <t>-1,13; 10,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 12,01</t>
+          <t>-2,27; 8,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,91; 400,89</t>
+          <t>33,78; 370,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 82,78</t>
+          <t>-31,46; 79,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 191,39</t>
+          <t>-18,63; 200,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 556,85</t>
+          <t>-28,93; 122,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-7,95%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,81</t>
+          <t>1,96; 6,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,88</t>
+          <t>1,55; 6,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,11</t>
+          <t>2,26; 7,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,0</t>
+          <t>-0,89; 3,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,06; 191,13</t>
+          <t>35,11; 179,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 125,0</t>
+          <t>19,85; 123,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,83; 181,47</t>
+          <t>38,22; 187,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 39,2</t>
+          <t>-14,06; 79,13</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,4</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-40,65%</t>
+          <t>-27,4%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,78</t>
+          <t>-0,09; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,11</t>
+          <t>-0,65; 6,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,07</t>
+          <t>0,24; 5,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,83</t>
+          <t>-5,14; 0,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 201,16</t>
+          <t>-5,12; 201,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 109,65</t>
+          <t>-6,72; 115,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 232,36</t>
+          <t>0,47; 209,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,46; -13,8</t>
+          <t>-52,99; 6,08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>344,55%</t>
+          <t>196,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,82</t>
+          <t>2,67; 6,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,03</t>
+          <t>1,91; 6,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,25</t>
+          <t>0,07; 5,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,86</t>
+          <t>0,89; 5,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,1; 2149,92</t>
+          <t>50,41; 2192,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,54; 456,17</t>
+          <t>34,35; 469,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 313,33</t>
+          <t>-1,88; 316,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 1787,23</t>
+          <t>1,57; 1988,56</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,45</t>
+          <t>2,08; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,69</t>
+          <t>2,15; 4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,17</t>
+          <t>1,73; 4,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,82</t>
+          <t>-0,4; 1,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,49; 119,69</t>
+          <t>46,17; 119,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,0; 85,61</t>
+          <t>32,19; 89,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,74; 97,83</t>
+          <t>31,26; 95,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 37,98</t>
+          <t>-6,29; 33,41</t>
         </is>
       </c>
     </row>
